--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU02/HRM/post DFS_HRM-2031-0120/Panel 02/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU02/HRM/post DFS_HRM-2031-0120/Panel 02/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Back_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.63798</v>
+        <v>16.76723</v>
       </c>
       <c r="D2" t="n">
-        <v>16.52518</v>
+        <v>16.52364</v>
       </c>
       <c r="E2" t="n">
-        <v>16.53554</v>
+        <v>16.58095</v>
       </c>
       <c r="F2" t="n">
-        <v>42.77256</v>
+        <v>42.93984</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0508</v>
+        <v>0.05026</v>
       </c>
       <c r="H2" t="n">
-        <v>1.79797</v>
+        <v>1.7921</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.6821</v>
+        <v>16.77425</v>
       </c>
       <c r="D3" t="n">
-        <v>16.49493</v>
+        <v>16.71453</v>
       </c>
       <c r="E3" t="n">
-        <v>16.5986</v>
+        <v>16.75854</v>
       </c>
       <c r="F3" t="n">
-        <v>42.88854</v>
+        <v>42.57686</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04981</v>
+        <v>0.05045</v>
       </c>
       <c r="H3" t="n">
-        <v>1.79682</v>
+        <v>1.83405</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.92117</v>
+        <v>16.83663</v>
       </c>
       <c r="D4" t="n">
-        <v>16.7936</v>
+        <v>16.66869</v>
       </c>
       <c r="E4" t="n">
-        <v>16.88707</v>
+        <v>16.8222</v>
       </c>
       <c r="F4" t="n">
-        <v>43.02961</v>
+        <v>42.67765</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05146</v>
+        <v>0.05078</v>
       </c>
       <c r="H4" t="n">
-        <v>1.82639</v>
+        <v>1.8107</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.58098</v>
+        <v>17.00059</v>
       </c>
       <c r="D5" t="n">
-        <v>16.70861</v>
+        <v>16.66394</v>
       </c>
       <c r="E5" t="n">
-        <v>16.8323</v>
+        <v>16.83435</v>
       </c>
       <c r="F5" t="n">
-        <v>43.02962</v>
+        <v>42.92885</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05086</v>
+        <v>0.05104</v>
       </c>
       <c r="H5" t="n">
-        <v>1.80464</v>
+        <v>1.82705</v>
       </c>
     </row>
     <row r="6">
@@ -559,23 +559,10 @@
           <t>Unit 5</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>16.8148</v>
-      </c>
-      <c r="D6" t="n">
-        <v>16.32985</v>
-      </c>
-      <c r="E6" t="n">
-        <v>16.65688</v>
-      </c>
-      <c r="F6" t="n">
-        <v>43.44036</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.05116</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1.79363</v>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>scratched - not measurable</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -585,22 +572,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.94401</v>
+        <v>16.71619</v>
       </c>
       <c r="D7" t="n">
-        <v>16.65005</v>
+        <v>16.54847</v>
       </c>
       <c r="E7" t="n">
-        <v>16.62407</v>
+        <v>16.67498</v>
       </c>
       <c r="F7" t="n">
-        <v>41.85011</v>
+        <v>42.0418</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05052</v>
+        <v>0.04998</v>
       </c>
       <c r="H7" t="n">
-        <v>1.80519</v>
+        <v>1.82425</v>
       </c>
     </row>
     <row r="8">
@@ -610,22 +597,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.8245</v>
+        <v>16.85619</v>
       </c>
       <c r="D8" t="n">
-        <v>16.37783</v>
+        <v>16.31291</v>
       </c>
       <c r="E8" t="n">
-        <v>16.7045</v>
+        <v>16.48406</v>
       </c>
       <c r="F8" t="n">
-        <v>42.14592</v>
+        <v>43.13711</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05041</v>
+        <v>0.05102</v>
       </c>
       <c r="H8" t="n">
-        <v>1.75999</v>
+        <v>1.79927</v>
       </c>
     </row>
     <row r="9">
@@ -635,22 +622,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.75492</v>
+        <v>16.83666</v>
       </c>
       <c r="D9" t="n">
-        <v>16.43244</v>
+        <v>16.65676</v>
       </c>
       <c r="E9" t="n">
-        <v>16.62645</v>
+        <v>16.66017</v>
       </c>
       <c r="F9" t="n">
-        <v>42.387</v>
+        <v>42.17636</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05124</v>
+        <v>0.05049</v>
       </c>
       <c r="H9" t="n">
-        <v>1.83886</v>
+        <v>1.82233</v>
       </c>
     </row>
     <row r="10">
@@ -660,386 +647,257 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.69195</v>
+        <v>16.90456</v>
       </c>
       <c r="D10" t="n">
-        <v>16.18612</v>
+        <v>16.5493</v>
       </c>
       <c r="E10" t="n">
-        <v>16.66466</v>
+        <v>16.5833</v>
       </c>
       <c r="F10" t="n">
-        <v>42.36887</v>
+        <v>43.9434</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05166</v>
+        <v>0.04994</v>
       </c>
       <c r="H10" t="n">
-        <v>1.82933</v>
+        <v>1.82943</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Pad 2</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>16.78131</v>
-      </c>
-      <c r="D11" t="n">
-        <v>16.67529</v>
-      </c>
-      <c r="E11" t="n">
-        <v>16.7556</v>
-      </c>
-      <c r="F11" t="n">
-        <v>42.47428</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.05059</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1.83809</v>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Trace 1</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>17.05222</v>
+        <v>16.71553</v>
       </c>
       <c r="D12" t="n">
-        <v>17.00673</v>
+        <v>15.81958</v>
       </c>
       <c r="E12" t="n">
-        <v>16.5852</v>
+        <v>16.22628</v>
       </c>
       <c r="F12" t="n">
-        <v>42.13097</v>
+        <v>21.74717</v>
       </c>
       <c r="G12" t="n">
-        <v>0.05056</v>
-      </c>
-      <c r="H12" t="n">
-        <v>1.80987</v>
+        <v>34.16635</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>16.78788</v>
+        <v>16.67701</v>
       </c>
       <c r="D13" t="n">
-        <v>16.8254</v>
+        <v>15.84017</v>
       </c>
       <c r="E13" t="n">
-        <v>16.5834</v>
+        <v>16.61372</v>
       </c>
       <c r="F13" t="n">
-        <v>43.76676</v>
+        <v>20.91276</v>
       </c>
       <c r="G13" t="n">
-        <v>0.05095</v>
-      </c>
-      <c r="H13" t="n">
-        <v>1.82323</v>
+        <v>34.66959</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>re-measured</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>16.6154</v>
+        <v>16.87696</v>
       </c>
       <c r="D14" t="n">
-        <v>16.64829</v>
+        <v>16.20743</v>
       </c>
       <c r="E14" t="n">
-        <v>17.07659</v>
+        <v>16.48772</v>
       </c>
       <c r="F14" t="n">
-        <v>42.3806</v>
+        <v>21.73725</v>
       </c>
       <c r="G14" t="n">
-        <v>0.05039</v>
-      </c>
-      <c r="H14" t="n">
-        <v>1.81354</v>
+        <v>34.0404</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>17.03834</v>
+        <v>16.77587</v>
       </c>
       <c r="D15" t="n">
-        <v>16.65723</v>
+        <v>15.91964</v>
       </c>
       <c r="E15" t="n">
-        <v>17.0123</v>
+        <v>16.75547</v>
       </c>
       <c r="F15" t="n">
-        <v>42.80374</v>
+        <v>20.94203</v>
       </c>
       <c r="G15" t="n">
-        <v>0.05094</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1.82993</v>
+        <v>34.80116</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>16.57574</v>
+        <v>16.60776</v>
       </c>
       <c r="D16" t="n">
-        <v>16.60915</v>
+        <v>16.1378</v>
       </c>
       <c r="E16" t="n">
-        <v>16.63218</v>
+        <v>16.47473</v>
       </c>
       <c r="F16" t="n">
-        <v>41.4593</v>
+        <v>21.51314</v>
       </c>
       <c r="G16" t="n">
-        <v>0.05069</v>
-      </c>
-      <c r="H16" t="n">
-        <v>1.80113</v>
+        <v>33.23298</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>16.80866</v>
+        <v>16.8475</v>
       </c>
       <c r="D17" t="n">
-        <v>16.72912</v>
+        <v>16.13238</v>
       </c>
       <c r="E17" t="n">
-        <v>16.61272</v>
+        <v>16.38374</v>
       </c>
       <c r="F17" t="n">
-        <v>42.30943</v>
+        <v>21.83128</v>
       </c>
       <c r="G17" t="n">
-        <v>0.04971</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1.80025</v>
+        <v>34.21392</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>16.7559</v>
+        <v>16.82151</v>
       </c>
       <c r="D18" t="n">
-        <v>16.61139</v>
+        <v>15.89368</v>
       </c>
       <c r="E18" t="n">
-        <v>16.62221</v>
+        <v>16.52899</v>
       </c>
       <c r="F18" t="n">
-        <v>42.93476</v>
+        <v>22.0671</v>
       </c>
       <c r="G18" t="n">
-        <v>0.05062</v>
-      </c>
-      <c r="H18" t="n">
-        <v>1.79287</v>
+        <v>34.42477</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>17.1759</v>
+      </c>
+      <c r="D19" t="n">
+        <v>15.9675</v>
+      </c>
+      <c r="E19" t="n">
+        <v>16.33117</v>
+      </c>
+      <c r="F19" t="n">
+        <v>21.66737</v>
+      </c>
+      <c r="G19" t="n">
+        <v>34.37899</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>Unit 3</t>
         </is>
       </c>
-      <c r="C19" t="n">
-        <v>16.85435</v>
-      </c>
-      <c r="D19" t="n">
-        <v>16.65523</v>
-      </c>
-      <c r="E19" t="n">
-        <v>17.0327</v>
-      </c>
-      <c r="F19" t="n">
-        <v>42.49726</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.05088</v>
-      </c>
-      <c r="H19" t="n">
-        <v>1.80097</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>via 1</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>0.59883</v>
-      </c>
-      <c r="D21" t="n">
-        <v>1.12968</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Unit 8</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>0.61861</v>
-      </c>
-      <c r="D22" t="n">
-        <v>1.11397</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Unit 9</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>0.6091299999999999</v>
-      </c>
-      <c r="D23" t="n">
-        <v>1.12572</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Unit 4</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>0.60581</v>
-      </c>
-      <c r="D24" t="n">
-        <v>1.13191</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Unit 5</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>0.61255</v>
-      </c>
-      <c r="D25" t="n">
-        <v>1.13427</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Unit 6</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>0.61752</v>
-      </c>
-      <c r="D26" t="n">
-        <v>1.11517</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Unit 1</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>0.6022999999999999</v>
-      </c>
-      <c r="D27" t="n">
-        <v>1.12207</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Unit 2</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>0.60165</v>
-      </c>
-      <c r="D28" t="n">
-        <v>1.09763</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Unit 3</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>0.60522</v>
-      </c>
-      <c r="D29" t="n">
-        <v>1.10304</v>
+      <c r="C20" t="n">
+        <v>16.81144</v>
+      </c>
+      <c r="D20" t="n">
+        <v>15.6325</v>
+      </c>
+      <c r="E20" t="n">
+        <v>16.52985</v>
+      </c>
+      <c r="F20" t="n">
+        <v>21.95118</v>
+      </c>
+      <c r="G20" t="n">
+        <v>35.07926</v>
       </c>
     </row>
   </sheetData>
